--- a/ui/frontend/public/samples/dineastra_daily_operations_template.xlsx
+++ b/ui/frontend/public/samples/dineastra_daily_operations_template.xlsx
@@ -499,7 +499,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Tuesday, chef's table at 8pm</t>
+          <t>Chef's table at 8pm</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Walk-in cover count down</t>
+          <t>Walk-in covers down on a wet evening</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Late opening, one task missed</t>
+          <t>Late opening; one task missed</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One row per banquet or event booking. Net and margin are computed from revenue and costs on load, so there is no margin column here.</t>
+          <t>One row per private dining or event booking. Net and margin are computed from revenue and costs on load, so there is no margin column here.</t>
         </is>
       </c>
     </row>
